--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/02_Open_Business_Decisions_Log.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/02_Open_Business_Decisions_Log.xlsx
@@ -530,6 +530,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -565,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>

--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/02_Open_Business_Decisions_Log.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/02_Open_Business_Decisions_Log.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Tribe + RIVR + Finance</t>
+          <t>Lumbee Tribe + RIVR + Finance</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>RIVR + Tribe</t>
+          <t>RIVR + Lumbee Tribe</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Affordable tier per award floor; consult Tribe on increases</t>
+          <t>Affordable tier per award floor; consult Lumbee Tribe on increases</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Number of dark strands reserved to the Tribe on the Tribal Assets</t>
+          <t>Number of dark strands reserved to the Lumbee Tribe on the Tribal Assets</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Annual fixed IRU/operating payment to the Tribe</t>
+          <t>Annual fixed IRU/operating payment to the Lumbee Tribe</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>[■ business decision — recommend allow with Tribe revenue participation]</t>
+          <t>[■ business decision — recommend allow with Lumbee Tribe revenue participation]</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Tribe reversion/step-in to customer relationships vs. RIVR retains</t>
+          <t>Lumbee Tribe reversion/step-in to customer relationships vs. RIVR retains</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Recommend Tribe reversionary right tied to Tribal Assets</t>
+          <t>Recommend Lumbee Tribe reversionary right tied to Tribal Assets</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
